--- a/Data/collapsed database manual cases/guerrero_collapsed_edited.xlsx
+++ b/Data/collapsed database manual cases/guerrero_collapsed_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jpzorrilla/Documents/GitHub/The-Mexican-municipal-elections-electoral-precinct-level-database/Data/collapsed database manual cases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB2EEAA6-DCA3-CB49-B69E-227917A51D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AF7E6B0-F26E-D84C-8B74-CFC8E13D0738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4480" yWindow="500" windowWidth="31360" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5791" uniqueCount="1224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5794" uniqueCount="1225">
   <si>
     <t>uniqueid</t>
   </si>
@@ -3708,6 +3708,9 @@
   </si>
   <si>
     <t>https://www.iepcgro.mx/proceso2021/repositorio/convenios_coaliciones_cand_comunes/convenio_coalicion_flexible_prd_pri.pdf</t>
+  </si>
+  <si>
+    <t>BASILIO FLORENTINO DIAZ</t>
   </si>
 </sst>
 </file>
@@ -4075,7 +4078,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S583"/>
+  <dimension ref="A1:S584"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.1640625" bestFit="1" customWidth="1"/>
@@ -29298,6 +29301,23 @@
         <v>1223</v>
       </c>
     </row>
+    <row r="584" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A584">
+        <v>12062</v>
+      </c>
+      <c r="B584">
+        <v>2021</v>
+      </c>
+      <c r="E584" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F584" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H584" t="s">
+        <v>1163</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S548" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="5">
